--- a/Data/EXCEL/Transfer/salemon/202206/8427-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/8427-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66736AD6-4779-4443-9F08-6C663A22E611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFD3644B-C352-4D1C-BD8C-665C912C6BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="8427-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1221,18 +1221,19 @@
   <dimension ref="A1:Q130"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="9.875" customWidth="1"/>
-    <col min="6" max="7" width="10.875" customWidth="1"/>
-    <col min="8" max="8" width="12.25" customWidth="1"/>
-    <col min="9" max="9" width="11.375" customWidth="1"/>
-    <col min="10" max="10" width="10.875" customWidth="1"/>
-    <col min="11" max="11" width="12.25" customWidth="1"/>
-    <col min="12" max="12" width="10.875" customWidth="1"/>
-    <col min="13" max="13" width="12.25" customWidth="1"/>
-    <col min="14" max="14" width="11.375" customWidth="1"/>
-    <col min="15" max="15" width="10.875" customWidth="1"/>
-    <col min="16" max="17" width="12.25" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="5" width="11.375" customWidth="1"/>
+    <col min="6" max="7" width="12.375" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="12.375" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="12.375" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
